--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/specific-finding-value-vs</t>
+    <t>http://qualityregistry.org/ValueSet/specific-finding-value-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -105,16 +105,16 @@
     <t>ValueSet URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/mtici-score-vs</t>
-  </si>
-  <si>
-    <t>http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs</t>
-  </si>
-  <si>
-    <t>http://tecnomod-um.org/ValueSet/carotid-stenosis-level-vs</t>
-  </si>
-  <si>
-    <t>http://tecnomod-um.org/ValueSet/hemorrhagic-transformation-type-vs</t>
+    <t>http://qualityregistry.org/ValueSet/mtici-score-vs</t>
+  </si>
+  <si>
+    <t>http://qualityregistry.org/ValueSet/atrial-fibrillation-or-flutter-vs</t>
+  </si>
+  <si>
+    <t>http://qualityregistry.org/ValueSet/carotid-stenosis-level-vs</t>
+  </si>
+  <si>
+    <t>http://qualityregistry.org/ValueSet/hemorrhagic-transformation-type-vs</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-value-vs.xlsx
+++ b/ValueSet-specific-finding-value-vs.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
